--- a/artfynd/A 65216-2021 artfynd.xlsx
+++ b/artfynd/A 65216-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65216-2021 artfynd.xlsx
+++ b/artfynd/A 65216-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1026,6 +1026,238 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121596449</v>
+      </c>
+      <c r="B5" t="n">
+        <v>74707</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>308</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>495174</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6647372</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre barrsumpskog.</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>barkfläkt björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121596462</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>495160</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6647435</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Äldre barrsumpskog.</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>

--- a/artfynd/A 65216-2021 artfynd.xlsx
+++ b/artfynd/A 65216-2021 artfynd.xlsx
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121596449</v>
+        <v>121596462</v>
       </c>
       <c r="B5" t="n">
-        <v>74707</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,21 +1049,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495174</v>
+        <v>495160</v>
       </c>
       <c r="R5" t="n">
-        <v>6647372</v>
+        <v>6647435</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121596462</v>
+        <v>121596449</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>74707</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,21 +1165,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495160</v>
+        <v>495174</v>
       </c>
       <c r="R6" t="n">
-        <v>6647435</v>
+        <v>6647372</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 65216-2021 artfynd.xlsx
+++ b/artfynd/A 65216-2021 artfynd.xlsx
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121596449</v>
+        <v>121596462</v>
       </c>
       <c r="B5" t="n">
-        <v>74714</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,21 +1049,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495174</v>
+        <v>495160</v>
       </c>
       <c r="R5" t="n">
-        <v>6647372</v>
+        <v>6647435</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121596462</v>
+        <v>121596449</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>74714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,21 +1165,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495160</v>
+        <v>495174</v>
       </c>
       <c r="R6" t="n">
-        <v>6647435</v>
+        <v>6647372</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 65216-2021 artfynd.xlsx
+++ b/artfynd/A 65216-2021 artfynd.xlsx
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121596462</v>
+        <v>121596449</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>74714</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,21 +1049,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495160</v>
+        <v>495174</v>
       </c>
       <c r="R5" t="n">
-        <v>6647435</v>
+        <v>6647372</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>barkfläkt björkhögstubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121596449</v>
+        <v>121596462</v>
       </c>
       <c r="B6" t="n">
-        <v>74714</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,21 +1165,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495174</v>
+        <v>495160</v>
       </c>
       <c r="R6" t="n">
-        <v>6647372</v>
+        <v>6647435</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>barkfläkt björkhögstubbe</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 65216-2021 artfynd.xlsx
+++ b/artfynd/A 65216-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1262,6 +1262,103 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128179376</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92257</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hörkälven , Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>495227</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6647395</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Björk, Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 65216-2021 artfynd.xlsx
+++ b/artfynd/A 65216-2021 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>128179376</v>
       </c>
       <c r="B7" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 65216-2021 artfynd.xlsx
+++ b/artfynd/A 65216-2021 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>128179376</v>
       </c>
       <c r="B7" t="n">
-        <v>92258</v>
+        <v>92259</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 65216-2021 artfynd.xlsx
+++ b/artfynd/A 65216-2021 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>128179376</v>
       </c>
       <c r="B7" t="n">
-        <v>92259</v>
+        <v>92267</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 65216-2021 artfynd.xlsx
+++ b/artfynd/A 65216-2021 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>128179376</v>
       </c>
       <c r="B7" t="n">
-        <v>92267</v>
+        <v>92359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 65216-2021 artfynd.xlsx
+++ b/artfynd/A 65216-2021 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>128179376</v>
       </c>
       <c r="B7" t="n">
-        <v>92359</v>
+        <v>92371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 65216-2021 artfynd.xlsx
+++ b/artfynd/A 65216-2021 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>128179376</v>
       </c>
       <c r="B7" t="n">
-        <v>92371</v>
+        <v>92373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 65216-2021 artfynd.xlsx
+++ b/artfynd/A 65216-2021 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>128179376</v>
       </c>
       <c r="B7" t="n">
-        <v>92373</v>
+        <v>92374</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 65216-2021 artfynd.xlsx
+++ b/artfynd/A 65216-2021 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>128179376</v>
       </c>
       <c r="B7" t="n">
-        <v>92374</v>
+        <v>92401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 65216-2021 artfynd.xlsx
+++ b/artfynd/A 65216-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90813269</v>
+        <v>121596449</v>
       </c>
       <c r="B2" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hörkälven, Vstm</t>
+          <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495247.118846097</v>
+        <v>495174</v>
       </c>
       <c r="R2" t="n">
-        <v>6647400.894427474</v>
+        <v>6647372</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,16 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Äldre barrsumpskog.</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>barkfläkt björkhögstubbe</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -796,58 +786,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90813270</v>
+        <v>121596450</v>
       </c>
       <c r="B3" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hörkälven, Vstm</t>
+          <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495269.7935801101</v>
+        <v>495150</v>
       </c>
       <c r="R3" t="n">
-        <v>6647480.98595211</v>
+        <v>6647372</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,16 +867,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre barrsumpskog.</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>barkfläkt björkhögstubbe</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -917,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82384287</v>
+        <v>121596461</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,37 +908,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hörkälven, Vstm</t>
+          <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495156.9101907275</v>
+        <v>495156</v>
       </c>
       <c r="R4" t="n">
-        <v>6647462.103676414</v>
+        <v>6647455</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-11-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-11-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,16 +978,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Äldre barrsumpskog.</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>barkfläkt björkhögstubbe</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jesper Hansson, Siverrt Juneholm</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1033,15 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121596462</v>
+        <v>128179376</v>
       </c>
       <c r="B5" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,37 +1019,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hörksälven, Vstm</t>
+          <t>Hörkälven , Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495160</v>
+        <v>495227</v>
       </c>
       <c r="R5" t="n">
-        <v>6647435</v>
+        <v>6647395</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,12 +1073,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,83 +1089,64 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Äldre barrsumpskog.</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>torrgran</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Anton Björk, Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121596449</v>
+        <v>82384287</v>
       </c>
       <c r="B6" t="n">
-        <v>74727</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hörksälven, Vstm</t>
+          <t>Hörkälven, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495174</v>
+        <v>495157</v>
       </c>
       <c r="R6" t="n">
-        <v>6647372</v>
+        <v>6647462</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,12 +1170,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2019-11-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2019-11-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,26 +1186,16 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Äldre barrsumpskog.</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>barkfläkt björkhögstubbe</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Jesper Hansson, Siverrt Juneholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1265,48 +1206,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128179376</v>
+        <v>121596462</v>
       </c>
       <c r="B7" t="n">
-        <v>92401</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4745</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hörkälven , Vstm</t>
+          <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495227</v>
+        <v>495160</v>
       </c>
       <c r="R7" t="n">
-        <v>6647395</v>
+        <v>6647435</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,12 +1271,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,19 +1287,890 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre barrsumpskog.</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Björk, Niklas Trogen</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121596460</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>495156</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6647455</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre barrsumpskog.</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>barkfläkt björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>90813095</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hörkälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>495134</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6647473</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121596451</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>495127</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6647348</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre blåbärstallskog.</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>90813255</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hörkälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>495252</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6647427</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-09-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-09-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>90813257</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hörkälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>495271</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6647413</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2020-09-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2020-09-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>90813103</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hörkälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>495183</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6647501</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>90813269</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hörkälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>495247</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6647401</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2020-09-23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2020-09-23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>90813270</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hörkälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>495270</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6647481</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2020-09-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2020-09-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 65216-2021 artfynd.xlsx
+++ b/artfynd/A 65216-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121596449</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121596450</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121596461</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128179376</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1203,6 +1228,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82384287</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121596462</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1425,6 +1460,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121596460</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1526,6 +1566,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90813095</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1642,6 +1687,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121596451</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90813255</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1853,6 +1908,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90813257</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1959,6 +2019,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90813103</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2065,6 +2130,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90813269</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2171,8 +2241,29 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90813270</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>